--- a/user_info.xlsx
+++ b/user_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\Excel\Task\Task2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6082F23-BF16-4FE8-9105-866CFFE79073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB793DDC-C765-4DCC-B0D1-70CCDC75C226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">Hello </t>
   </si>
   <si>
     <t>World</t>
+  </si>
+  <si>
+    <t>yerugfvbn</t>
+  </si>
+  <si>
+    <t>hlgufytdxgfcgvh</t>
   </si>
 </sst>
 </file>
@@ -343,17 +349,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
